--- a/cet4/result/77_新闻女神_战地玫瑰的传奇/77_新闻女神_战地玫瑰的传奇_学习版.xlsx
+++ b/cet4/result/77_新闻女神_战地玫瑰的传奇/77_新闻女神_战地玫瑰的传奇_学习版.xlsx
@@ -397,829 +397,773 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D54"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>outskirt</v>
       </c>
       <c r="B2" t="str">
-        <v>outskirt</v>
+        <v>/'aʊt,skɜːrt/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>郊区</v>
       </c>
-      <c r="D2" t="str">
-        <v>outskirt(郊区)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>eager</v>
       </c>
       <c r="B3" t="str">
-        <v>eager</v>
+        <v>/ˈiːɡər/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>渴望</v>
       </c>
-      <c r="D3" t="str">
-        <v>eager(渴望)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>correspondent</v>
       </c>
       <c r="B4" t="str">
-        <v>correspondent</v>
+        <v>/ˌkɔːrəˈspɑːndənt/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>通讯记者</v>
       </c>
-      <c r="D4" t="str">
-        <v>correspondent(通讯记者)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>indispensable</v>
       </c>
       <c r="B5" t="str">
-        <v>indispensable</v>
+        <v>/ˌɪndɪˈspensəbl/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>不可缺少的</v>
       </c>
-      <c r="D5" t="str">
-        <v>indispensable(不可缺少的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>Angle</v>
       </c>
       <c r="B6" t="str">
-        <v>Angle</v>
+        <v>/ˈæŋɡl/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>盎格鲁</v>
       </c>
-      <c r="D6" t="str">
-        <v>Angle(盎格鲁)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>geography</v>
       </c>
       <c r="B7" t="str">
-        <v>geography</v>
+        <v>/dʒiˈɑːɡrəfi/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>地理</v>
       </c>
-      <c r="D7" t="str">
-        <v>geography(地理)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>history</v>
       </c>
       <c r="B8" t="str">
-        <v>history</v>
+        <v>/ˈhɪstri/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>历史</v>
       </c>
-      <c r="D8" t="str">
-        <v>history(历史)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>agent</v>
       </c>
       <c r="B9" t="str">
-        <v>agent</v>
+        <v>/ˈeɪdʒənt/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>代理人</v>
       </c>
-      <c r="D9" t="str">
-        <v>agent(代理人)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>heroine</v>
       </c>
       <c r="B10" t="str">
-        <v>heroine</v>
+        <v>/ˈheroʊɪn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>女英雄</v>
       </c>
-      <c r="D10" t="str">
-        <v>heroine(女英雄)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>device</v>
       </c>
       <c r="B11" t="str">
-        <v>device</v>
+        <v>/dɪˈvaɪs/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>设备</v>
       </c>
-      <c r="D11" t="str">
-        <v>device(设备)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>model</v>
       </c>
       <c r="B12" t="str">
-        <v>model</v>
+        <v>/ˈmɑːdl/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>模范</v>
       </c>
-      <c r="D12" t="str">
-        <v>model(模范)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>ground</v>
       </c>
       <c r="B13" t="str">
-        <v>ground</v>
+        <v>/ɡraʊnd/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>地面</v>
       </c>
-      <c r="D13" t="str">
-        <v>ground(地面)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>prior</v>
       </c>
       <c r="B14" t="str">
-        <v>prior</v>
+        <v>/ˈpraɪər/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D14" t="str">
         <v>预先</v>
       </c>
-      <c r="D14" t="str">
-        <v>prior(预先)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>shirt</v>
       </c>
       <c r="B15" t="str">
-        <v>shirt</v>
+        <v>/ʃɜːrt/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>衬衫</v>
       </c>
-      <c r="D15" t="str">
-        <v>shirt(衬衫)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>teenager</v>
       </c>
       <c r="B16" t="str">
-        <v>teenager</v>
+        <v>/ˈtiːneɪdʒər/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>青少年</v>
       </c>
-      <c r="D16" t="str">
-        <v>teenager(青少年)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>split</v>
       </c>
       <c r="B17" t="str">
-        <v>split</v>
+        <v>/splɪt/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>分离</v>
       </c>
-      <c r="D17" t="str">
-        <v>split(分离)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>captain</v>
       </c>
       <c r="B18" t="str">
-        <v>captain</v>
+        <v>/ˈkæptɪn/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>队长</v>
       </c>
-      <c r="D18" t="str">
-        <v>captain(队长)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>conceal</v>
       </c>
       <c r="B19" t="str">
-        <v>conceal</v>
+        <v>/kənˈsiːl/</v>
       </c>
       <c r="C19" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D19" t="str">
         <v>隐瞒</v>
       </c>
-      <c r="D19" t="str">
-        <v>conceal(隐瞒)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>luxury</v>
       </c>
       <c r="B20" t="str">
-        <v>luxury</v>
+        <v>/ˈlʌkʃəri/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>奢侈</v>
       </c>
-      <c r="D20" t="str">
-        <v>luxury(奢侈)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>share</v>
       </c>
       <c r="B21" t="str">
-        <v>share</v>
+        <v>/ʃer/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D21" t="str">
         <v>分享</v>
       </c>
-      <c r="D21" t="str">
-        <v>share(分享)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>finally</v>
       </c>
       <c r="B22" t="str">
-        <v>finally</v>
+        <v>/ˈfaɪnəli/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D22" t="str">
         <v>最后</v>
       </c>
-      <c r="D22" t="str">
-        <v>finally(最后)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>cucumber</v>
       </c>
       <c r="B23" t="str">
-        <v>cucumber</v>
+        <v>/ˈkjuːkʌmbər/</v>
       </c>
       <c r="C23" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>黄瓜</v>
       </c>
-      <c r="D23" t="str">
-        <v>cucumber(黄瓜)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>delegation</v>
       </c>
       <c r="B24" t="str">
-        <v>delegation</v>
+        <v>/ˌdelɪˈɡeɪʃn/</v>
       </c>
       <c r="C24" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>代表团</v>
       </c>
-      <c r="D24" t="str">
-        <v>delegation(代表团)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>schedule</v>
       </c>
       <c r="B25" t="str">
-        <v>schedule</v>
+        <v>/ˈskedʒuːl/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D25" t="str">
         <v>时间表</v>
       </c>
-      <c r="D25" t="str">
-        <v>schedule(时间表)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>arrange</v>
       </c>
       <c r="B26" t="str">
-        <v>arrange</v>
+        <v>/əˈreɪndʒ/</v>
       </c>
       <c r="C26" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D26" t="str">
         <v>安排</v>
       </c>
-      <c r="D26" t="str">
-        <v>arrange(安排)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>philosopher</v>
       </c>
       <c r="B27" t="str">
-        <v>philosopher</v>
+        <v>/fəˈlɑːsəfər/</v>
       </c>
       <c r="C27" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>哲学家</v>
       </c>
-      <c r="D27" t="str">
-        <v>philosopher(哲学家)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>liberation</v>
       </c>
       <c r="B28" t="str">
-        <v>liberation</v>
+        <v>/ˌlɪbəˈreɪʃn/</v>
       </c>
       <c r="C28" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>解放</v>
       </c>
-      <c r="D28" t="str">
-        <v>liberation(解放)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>there</v>
       </c>
       <c r="B29" t="str">
-        <v>there</v>
+        <v>/ðer/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./v./adv./int.</v>
+      </c>
+      <c r="D29" t="str">
         <v>在那边</v>
       </c>
-      <c r="D29" t="str">
-        <v>there(在那边)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>view</v>
       </c>
       <c r="B30" t="str">
-        <v>view</v>
+        <v>/vjuː/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D30" t="str">
         <v>视野</v>
       </c>
-      <c r="D30" t="str">
-        <v>view(视野)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>breath</v>
       </c>
       <c r="B31" t="str">
-        <v>breath</v>
+        <v>/breθ/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>气息</v>
       </c>
-      <c r="D31" t="str">
-        <v>breath(气息)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>aircraft</v>
       </c>
       <c r="B32" t="str">
-        <v>aircraft</v>
+        <v>/ˈerkræft/</v>
       </c>
       <c r="C32" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>飞机</v>
       </c>
-      <c r="D32" t="str">
-        <v>aircraft(飞机)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>electric</v>
       </c>
       <c r="B33" t="str">
-        <v>electric</v>
+        <v>/ɪˈlektrɪk/</v>
       </c>
       <c r="C33" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D33" t="str">
         <v>电动</v>
       </c>
-      <c r="D33" t="str">
-        <v>electric(电动)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>tremble</v>
       </c>
       <c r="B34" t="str">
-        <v>tremble</v>
+        <v>/ˈtrembl/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D34" t="str">
         <v>颤抖</v>
       </c>
-      <c r="D34" t="str">
-        <v>tremble(颤抖)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>submit</v>
       </c>
       <c r="B35" t="str">
-        <v>submit</v>
+        <v>/səbˈmɪt/</v>
       </c>
       <c r="C35" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D35" t="str">
         <v>提交</v>
       </c>
-      <c r="D35" t="str">
-        <v>submit(提交)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>reply</v>
       </c>
       <c r="B36" t="str">
-        <v>reply</v>
+        <v>/rɪˈplaɪ/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D36" t="str">
         <v>回复</v>
       </c>
-      <c r="D36" t="str">
-        <v>reply(回复)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>beneficial</v>
       </c>
       <c r="B37" t="str">
-        <v>beneficial</v>
+        <v>/ˌbenɪˈfɪʃl/</v>
       </c>
       <c r="C37" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D37" t="str">
         <v>有益的</v>
       </c>
-      <c r="D37" t="str">
-        <v>beneficial(有益的)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>expert</v>
       </c>
       <c r="B38" t="str">
-        <v>expert</v>
+        <v>/ˈekspɜːrt/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D38" t="str">
         <v>专家</v>
       </c>
-      <c r="D38" t="str">
-        <v>expert(专家)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>saint</v>
       </c>
       <c r="B39" t="str">
-        <v>saint</v>
+        <v>/seɪnt/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D39" t="str">
         <v>圣徒</v>
       </c>
-      <c r="D39" t="str">
-        <v>saint(圣徒)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>congratulate</v>
       </c>
       <c r="B40" t="str">
-        <v>congratulate</v>
+        <v>/kənˈɡrætʃuleɪt/</v>
       </c>
       <c r="C40" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D40" t="str">
         <v>祝贺</v>
       </c>
-      <c r="D40" t="str">
-        <v>congratulate(祝贺)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>golf</v>
       </c>
       <c r="B41" t="str">
-        <v>golf</v>
+        <v>/ɡɑːlf/</v>
       </c>
       <c r="C41" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D41" t="str">
         <v>高尔夫</v>
       </c>
-      <c r="D41" t="str">
-        <v>golf(高尔夫)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>blossom</v>
       </c>
       <c r="B42" t="str">
-        <v>blossom</v>
+        <v>/ˈblɑːsəm/</v>
       </c>
       <c r="C42" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D42" t="str">
         <v>花</v>
       </c>
-      <c r="D42" t="str">
-        <v>blossom(花)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>start</v>
       </c>
       <c r="B43" t="str">
-        <v>start</v>
+        <v>/stɑːrt/</v>
       </c>
       <c r="C43" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D43" t="str">
         <v>开始</v>
       </c>
-      <c r="D43" t="str">
-        <v>start(开始)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>rational</v>
       </c>
       <c r="B44" t="str">
-        <v>rational</v>
+        <v>/ˈræʃnəl/</v>
       </c>
       <c r="C44" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D44" t="str">
         <v>理性</v>
       </c>
-      <c r="D44" t="str">
-        <v>rational(理性)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>music</v>
       </c>
       <c r="B45" t="str">
-        <v>music</v>
+        <v>/ˈmjuːzɪk/</v>
       </c>
       <c r="C45" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>音乐</v>
       </c>
-      <c r="D45" t="str">
-        <v>music(音乐)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>several</v>
       </c>
       <c r="B46" t="str">
-        <v>blossom</v>
+        <v>/ˈsevrəl/</v>
       </c>
       <c r="C46" t="str">
-        <v>花</v>
+        <v>n./adj./pron.</v>
       </c>
       <c r="D46" t="str">
-        <v>blossom(花)📢</v>
+        <v>几个</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>cross</v>
       </c>
       <c r="B47" t="str">
-        <v>several</v>
+        <v>/krɔːs/</v>
       </c>
       <c r="C47" t="str">
-        <v>几个</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D47" t="str">
-        <v>several(几个)📢</v>
+        <v>十字架</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>trunk</v>
       </c>
       <c r="B48" t="str">
-        <v>cross</v>
+        <v>/trʌŋk/</v>
       </c>
       <c r="C48" t="str">
-        <v>十字架</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>cross(十字架)📢</v>
+        <v>树干</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>specimen</v>
       </c>
       <c r="B49" t="str">
-        <v>trunk</v>
+        <v>/ˈspesɪmən/</v>
       </c>
       <c r="C49" t="str">
-        <v>树干</v>
+        <v>n.</v>
       </c>
       <c r="D49" t="str">
-        <v>trunk(树干)📢</v>
+        <v>标本</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>faith</v>
       </c>
       <c r="B50" t="str">
-        <v>specimen</v>
+        <v>/feɪθ/</v>
       </c>
       <c r="C50" t="str">
-        <v>标本</v>
+        <v>n.</v>
       </c>
       <c r="D50" t="str">
-        <v>specimen(标本)📢</v>
+        <v>信仰</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>favourable</v>
       </c>
       <c r="B51" t="str">
-        <v>faith</v>
+        <v>/ˈfeɪvərəbl/</v>
       </c>
       <c r="C51" t="str">
-        <v>信仰</v>
+        <v>adj.</v>
       </c>
       <c r="D51" t="str">
-        <v>faith(信仰)📢</v>
+        <v>有利的</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>worthwhile</v>
       </c>
       <c r="B52" t="str">
-        <v>rational</v>
+        <v>/ˌwɜːrθˈwaɪl/</v>
       </c>
       <c r="C52" t="str">
-        <v>理性</v>
+        <v>adj.</v>
       </c>
       <c r="D52" t="str">
-        <v>rational(理性)📢</v>
+        <v>值得的</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>reserve</v>
       </c>
       <c r="B53" t="str">
-        <v>favourable</v>
+        <v>/rɪˈzɜːrv/</v>
       </c>
       <c r="C53" t="str">
-        <v>有利的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D53" t="str">
-        <v>favourable(有利的)📢</v>
+        <v>预备队</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>53</v>
+      <c r="A54" t="str">
+        <v>hint</v>
       </c>
       <c r="B54" t="str">
-        <v>worthwhile</v>
+        <v>/hɪnt/</v>
       </c>
       <c r="C54" t="str">
-        <v>值得的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D54" t="str">
-        <v>worthwhile(值得的)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>reserve</v>
-      </c>
-      <c r="C55" t="str">
-        <v>预备队</v>
-      </c>
-      <c r="D55" t="str">
-        <v>reserve(预备队)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>hint</v>
-      </c>
-      <c r="C56" t="str">
         <v>暗示</v>
-      </c>
-      <c r="D56" t="str">
-        <v>hint(暗示)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>faith</v>
-      </c>
-      <c r="C57" t="str">
-        <v>信仰</v>
-      </c>
-      <c r="D57" t="str">
-        <v>faith(信仰)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>indispensable</v>
-      </c>
-      <c r="C58" t="str">
-        <v>不可缺少的</v>
-      </c>
-      <c r="D58" t="str">
-        <v>indispensable(不可缺少的)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D54"/>
   </ignoredErrors>
 </worksheet>
 </file>